--- a/artfynd/A 367-2024 artfynd.xlsx
+++ b/artfynd/A 367-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134135927</v>
+        <v>134135933</v>
       </c>
       <c r="B2" t="n">
-        <v>58136</v>
+        <v>92231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574156</v>
+        <v>574181</v>
       </c>
       <c r="R2" t="n">
-        <v>7150451</v>
+        <v>7150475</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134135947</v>
+        <v>134135927</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>58136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,34 +793,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574258</v>
+        <v>574156</v>
       </c>
       <c r="R3" t="n">
-        <v>7150736</v>
+        <v>7150451</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134135933</v>
+        <v>134135947</v>
       </c>
       <c r="B4" t="n">
-        <v>92231</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574181</v>
+        <v>574258</v>
       </c>
       <c r="R4" t="n">
-        <v>7150475</v>
+        <v>7150736</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134135924</v>
+        <v>134135934</v>
       </c>
       <c r="B5" t="n">
-        <v>58410</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,43 +1016,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574156</v>
+        <v>574184</v>
       </c>
       <c r="R5" t="n">
-        <v>7150461</v>
+        <v>7150477</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134135934</v>
+        <v>134135924</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>58410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,34 +1123,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574184</v>
+        <v>574156</v>
       </c>
       <c r="R6" t="n">
-        <v>7150477</v>
+        <v>7150461</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134135917</v>
+        <v>134135937</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,39 +1346,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574134</v>
+        <v>574222</v>
       </c>
       <c r="R8" t="n">
-        <v>7150487</v>
+        <v>7150559</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1410,7 +1405,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1420,7 +1415,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1554,10 +1549,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134135937</v>
+        <v>134135917</v>
       </c>
       <c r="B10" t="n">
-        <v>79359</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,34 +1560,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574222</v>
+        <v>574134</v>
       </c>
       <c r="R10" t="n">
-        <v>7150559</v>
+        <v>7150487</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,32 +1661,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134135939</v>
+        <v>134135908</v>
       </c>
       <c r="B11" t="n">
-        <v>78718</v>
+        <v>79359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574223</v>
+        <v>574266</v>
       </c>
       <c r="R11" t="n">
-        <v>7150560</v>
+        <v>7150700</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,32 +1768,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134135940</v>
+        <v>134135939</v>
       </c>
       <c r="B12" t="n">
-        <v>83208</v>
+        <v>78718</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574229</v>
+        <v>574223</v>
       </c>
       <c r="R12" t="n">
         <v>7150560</v>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1875,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134135908</v>
+        <v>134135940</v>
       </c>
       <c r="B13" t="n">
-        <v>79359</v>
+        <v>83208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1886,21 +1886,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574266</v>
+        <v>574229</v>
       </c>
       <c r="R13" t="n">
-        <v>7150700</v>
+        <v>7150560</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2303,7 +2303,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134135941</v>
+        <v>134135929</v>
       </c>
       <c r="B17" t="n">
         <v>79359</v>
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574230</v>
+        <v>574169</v>
       </c>
       <c r="R17" t="n">
-        <v>7150560</v>
+        <v>7150449</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2410,7 +2410,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134135929</v>
+        <v>134135941</v>
       </c>
       <c r="B18" t="n">
         <v>79359</v>
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574169</v>
+        <v>574230</v>
       </c>
       <c r="R18" t="n">
-        <v>7150449</v>
+        <v>7150560</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,7 +2517,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134135911</v>
+        <v>134135945</v>
       </c>
       <c r="B19" t="n">
         <v>79359</v>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574260</v>
+        <v>574227</v>
       </c>
       <c r="R19" t="n">
-        <v>7150657</v>
+        <v>7150576</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,7 +2624,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134135945</v>
+        <v>134135911</v>
       </c>
       <c r="B20" t="n">
         <v>79359</v>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574227</v>
+        <v>574260</v>
       </c>
       <c r="R20" t="n">
-        <v>7150576</v>
+        <v>7150657</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2945,45 +2945,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134135905</v>
+        <v>134135936</v>
       </c>
       <c r="B23" t="n">
-        <v>79359</v>
+        <v>58079</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574318</v>
+        <v>574224</v>
       </c>
       <c r="R23" t="n">
-        <v>7150754</v>
+        <v>7150555</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3015,7 +3024,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3025,7 +3034,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3052,10 +3061,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134135912</v>
+        <v>134135925</v>
       </c>
       <c r="B24" t="n">
-        <v>79359</v>
+        <v>83208</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3063,21 +3072,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3087,10 +3096,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574254</v>
+        <v>574151</v>
       </c>
       <c r="R24" t="n">
-        <v>7150573</v>
+        <v>7150432</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3122,7 +3131,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3132,7 +3141,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3159,54 +3168,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134135936</v>
+        <v>134135912</v>
       </c>
       <c r="B25" t="n">
-        <v>58079</v>
+        <v>79359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574224</v>
+        <v>574254</v>
       </c>
       <c r="R25" t="n">
-        <v>7150555</v>
+        <v>7150573</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3275,10 +3275,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134135925</v>
+        <v>134135905</v>
       </c>
       <c r="B26" t="n">
-        <v>83208</v>
+        <v>79359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3286,21 +3286,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574151</v>
+        <v>574318</v>
       </c>
       <c r="R26" t="n">
-        <v>7150432</v>
+        <v>7150754</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3382,10 +3382,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134135918</v>
+        <v>134135949</v>
       </c>
       <c r="B27" t="n">
-        <v>79359</v>
+        <v>83208</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3393,21 +3393,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574130</v>
+        <v>574260</v>
       </c>
       <c r="R27" t="n">
-        <v>7150486</v>
+        <v>7150754</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3703,10 +3703,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134135949</v>
+        <v>134135918</v>
       </c>
       <c r="B30" t="n">
-        <v>83208</v>
+        <v>79359</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574260</v>
+        <v>574130</v>
       </c>
       <c r="R30" t="n">
-        <v>7150754</v>
+        <v>7150486</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3810,7 +3810,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134135943</v>
+        <v>134135921</v>
       </c>
       <c r="B31" t="n">
         <v>79359</v>
@@ -3845,10 +3845,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574228</v>
+        <v>574121</v>
       </c>
       <c r="R31" t="n">
-        <v>7150569</v>
+        <v>7150461</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3917,10 +3917,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134135935</v>
+        <v>134135943</v>
       </c>
       <c r="B32" t="n">
-        <v>78368</v>
+        <v>79359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3928,21 +3928,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574222</v>
+        <v>574228</v>
       </c>
       <c r="R32" t="n">
-        <v>7150554</v>
+        <v>7150569</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4024,10 +4024,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134135921</v>
+        <v>134135935</v>
       </c>
       <c r="B33" t="n">
-        <v>79359</v>
+        <v>78368</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4035,21 +4035,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574121</v>
+        <v>574222</v>
       </c>
       <c r="R33" t="n">
-        <v>7150461</v>
+        <v>7150554</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4131,10 +4131,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134135915</v>
+        <v>134135909</v>
       </c>
       <c r="B34" t="n">
-        <v>79359</v>
+        <v>58678</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4142,34 +4142,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>103056</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574168</v>
+        <v>574325</v>
       </c>
       <c r="R34" t="n">
-        <v>7150497</v>
+        <v>7150650</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4201,7 +4210,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4211,7 +4220,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4238,7 +4247,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134135931</v>
+        <v>134135923</v>
       </c>
       <c r="B35" t="n">
         <v>79359</v>
@@ -4273,10 +4282,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574171</v>
+        <v>574134</v>
       </c>
       <c r="R35" t="n">
-        <v>7150453</v>
+        <v>7150457</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4308,7 +4317,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4318,7 +4327,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4345,10 +4354,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134135909</v>
+        <v>134135931</v>
       </c>
       <c r="B36" t="n">
-        <v>58678</v>
+        <v>79359</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4356,43 +4365,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103056</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574325</v>
+        <v>574171</v>
       </c>
       <c r="R36" t="n">
-        <v>7150650</v>
+        <v>7150453</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4461,7 +4461,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134135923</v>
+        <v>134135915</v>
       </c>
       <c r="B37" t="n">
         <v>79359</v>
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574134</v>
+        <v>574168</v>
       </c>
       <c r="R37" t="n">
-        <v>7150457</v>
+        <v>7150497</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4782,45 +4782,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134135928</v>
+        <v>134135910</v>
       </c>
       <c r="B40" t="n">
-        <v>91960</v>
+        <v>58519</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>102990</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574159</v>
+        <v>574267</v>
       </c>
       <c r="R40" t="n">
-        <v>7150451</v>
+        <v>7150654</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4852,7 +4861,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4862,7 +4871,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4889,54 +4898,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134135910</v>
+        <v>134135928</v>
       </c>
       <c r="B41" t="n">
-        <v>58519</v>
+        <v>91960</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102990</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574267</v>
+        <v>574159</v>
       </c>
       <c r="R41" t="n">
-        <v>7150654</v>
+        <v>7150451</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 367-2024 artfynd.xlsx
+++ b/artfynd/A 367-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134135933</v>
       </c>
       <c r="B2" t="n">
-        <v>92231</v>
+        <v>92238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>134135947</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>134135934</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>134135946</v>
       </c>
       <c r="B7" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>134135937</v>
       </c>
       <c r="B8" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134135906</v>
+        <v>134135917</v>
       </c>
       <c r="B9" t="n">
-        <v>79359</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,34 +1453,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574296</v>
+        <v>574134</v>
       </c>
       <c r="R9" t="n">
-        <v>7150727</v>
+        <v>7150487</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1512,7 +1517,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1522,7 +1527,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134135917</v>
+        <v>134135906</v>
       </c>
       <c r="B10" t="n">
-        <v>57972</v>
+        <v>79366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,39 +1565,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574134</v>
+        <v>574296</v>
       </c>
       <c r="R10" t="n">
-        <v>7150487</v>
+        <v>7150727</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,32 +1661,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134135908</v>
+        <v>134135939</v>
       </c>
       <c r="B11" t="n">
-        <v>79359</v>
+        <v>78725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574266</v>
+        <v>574223</v>
       </c>
       <c r="R11" t="n">
-        <v>7150700</v>
+        <v>7150560</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,32 +1768,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134135939</v>
+        <v>134135908</v>
       </c>
       <c r="B12" t="n">
-        <v>78718</v>
+        <v>79366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574223</v>
+        <v>574266</v>
       </c>
       <c r="R12" t="n">
-        <v>7150560</v>
+        <v>7150700</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,7 +1878,7 @@
         <v>134135940</v>
       </c>
       <c r="B13" t="n">
-        <v>83208</v>
+        <v>83215</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>134135942</v>
       </c>
       <c r="B14" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>134135913</v>
       </c>
       <c r="B15" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>134135926</v>
       </c>
       <c r="B16" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>134135929</v>
       </c>
       <c r="B17" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>134135941</v>
       </c>
       <c r="B18" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,10 +2517,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134135945</v>
+        <v>134135911</v>
       </c>
       <c r="B19" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574227</v>
+        <v>574260</v>
       </c>
       <c r="R19" t="n">
-        <v>7150576</v>
+        <v>7150657</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,10 +2624,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134135911</v>
+        <v>134135945</v>
       </c>
       <c r="B20" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574260</v>
+        <v>574227</v>
       </c>
       <c r="R20" t="n">
-        <v>7150657</v>
+        <v>7150576</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2734,7 +2734,7 @@
         <v>134135951</v>
       </c>
       <c r="B21" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,10 +2838,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134135930</v>
+        <v>134135912</v>
       </c>
       <c r="B22" t="n">
-        <v>83349</v>
+        <v>79366</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2849,21 +2849,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574173</v>
+        <v>574254</v>
       </c>
       <c r="R22" t="n">
-        <v>7150455</v>
+        <v>7150573</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2945,54 +2945,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134135936</v>
+        <v>134135925</v>
       </c>
       <c r="B23" t="n">
-        <v>58079</v>
+        <v>83215</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574224</v>
+        <v>574151</v>
       </c>
       <c r="R23" t="n">
-        <v>7150555</v>
+        <v>7150432</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3024,7 +3015,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3034,7 +3025,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3061,10 +3052,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134135925</v>
+        <v>134135930</v>
       </c>
       <c r="B24" t="n">
-        <v>83208</v>
+        <v>83356</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3072,21 +3063,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>1467</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3096,10 +3087,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574151</v>
+        <v>574173</v>
       </c>
       <c r="R24" t="n">
-        <v>7150432</v>
+        <v>7150455</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3131,7 +3122,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3141,7 +3132,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3168,45 +3159,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134135912</v>
+        <v>134135936</v>
       </c>
       <c r="B25" t="n">
-        <v>79359</v>
+        <v>58079</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574254</v>
+        <v>574224</v>
       </c>
       <c r="R25" t="n">
-        <v>7150573</v>
+        <v>7150555</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3278,7 +3278,7 @@
         <v>134135905</v>
       </c>
       <c r="B26" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3382,10 +3382,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134135949</v>
+        <v>134135907</v>
       </c>
       <c r="B27" t="n">
-        <v>83208</v>
+        <v>79366</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3393,21 +3393,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574260</v>
+        <v>574313</v>
       </c>
       <c r="R27" t="n">
-        <v>7150754</v>
+        <v>7150743</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3489,10 +3489,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134135916</v>
+        <v>134135949</v>
       </c>
       <c r="B28" t="n">
-        <v>91960</v>
+        <v>83215</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3500,21 +3500,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574136</v>
+        <v>574260</v>
       </c>
       <c r="R28" t="n">
-        <v>7150487</v>
+        <v>7150754</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3596,10 +3596,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134135907</v>
+        <v>134135916</v>
       </c>
       <c r="B29" t="n">
-        <v>79359</v>
+        <v>91967</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574313</v>
+        <v>574136</v>
       </c>
       <c r="R29" t="n">
-        <v>7150743</v>
+        <v>7150487</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3706,7 +3706,7 @@
         <v>134135918</v>
       </c>
       <c r="B30" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>134135921</v>
       </c>
       <c r="B31" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>134135943</v>
       </c>
       <c r="B32" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>134135935</v>
       </c>
       <c r="B33" t="n">
-        <v>78368</v>
+        <v>78375</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4131,10 +4131,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134135909</v>
+        <v>134135931</v>
       </c>
       <c r="B34" t="n">
-        <v>58678</v>
+        <v>79366</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4142,43 +4142,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103056</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574325</v>
+        <v>574171</v>
       </c>
       <c r="R34" t="n">
-        <v>7150650</v>
+        <v>7150453</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4210,7 +4201,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4220,7 +4211,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4250,7 +4241,7 @@
         <v>134135923</v>
       </c>
       <c r="B35" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4354,10 +4345,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134135931</v>
+        <v>134135909</v>
       </c>
       <c r="B36" t="n">
-        <v>79359</v>
+        <v>58678</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4365,34 +4356,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103056</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574171</v>
+        <v>574325</v>
       </c>
       <c r="R36" t="n">
-        <v>7150453</v>
+        <v>7150650</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4464,7 +4464,7 @@
         <v>134135915</v>
       </c>
       <c r="B37" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>134135950</v>
       </c>
       <c r="B38" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>134135922</v>
       </c>
       <c r="B39" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4782,54 +4782,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134135910</v>
+        <v>134135928</v>
       </c>
       <c r="B40" t="n">
-        <v>58519</v>
+        <v>91967</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102990</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574267</v>
+        <v>574159</v>
       </c>
       <c r="R40" t="n">
-        <v>7150654</v>
+        <v>7150451</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4861,7 +4852,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4871,7 +4862,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4898,45 +4889,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134135928</v>
+        <v>134135910</v>
       </c>
       <c r="B41" t="n">
-        <v>91960</v>
+        <v>58519</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>102990</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574159</v>
+        <v>574267</v>
       </c>
       <c r="R41" t="n">
-        <v>7150451</v>
+        <v>7150654</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5008,7 +5008,7 @@
         <v>134135914</v>
       </c>
       <c r="B42" t="n">
-        <v>96399</v>
+        <v>96406</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 367-2024 artfynd.xlsx
+++ b/artfynd/A 367-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134135933</v>
+        <v>134135939</v>
       </c>
       <c r="B2" t="n">
-        <v>92238</v>
+        <v>78732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574181</v>
+        <v>574223</v>
       </c>
       <c r="R2" t="n">
-        <v>7150475</v>
+        <v>7150560</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134135927</v>
+        <v>134135933</v>
       </c>
       <c r="B3" t="n">
-        <v>58136</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,43 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574156</v>
+        <v>574181</v>
       </c>
       <c r="R3" t="n">
-        <v>7150451</v>
+        <v>7150475</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134135947</v>
+        <v>134135916</v>
       </c>
       <c r="B4" t="n">
-        <v>79366</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574258</v>
+        <v>574136</v>
       </c>
       <c r="R4" t="n">
-        <v>7150736</v>
+        <v>7150487</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -968,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134135934</v>
+        <v>134135928</v>
       </c>
       <c r="B5" t="n">
-        <v>79366</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574184</v>
+        <v>574159</v>
       </c>
       <c r="R5" t="n">
-        <v>7150477</v>
+        <v>7150451</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1075,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,54 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134135924</v>
+        <v>75330831</v>
       </c>
       <c r="B6" t="n">
-        <v>58410</v>
+        <v>91923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103001</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574156</v>
+        <v>574385</v>
       </c>
       <c r="R6" t="n">
-        <v>7150461</v>
+        <v>7150759</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1186,22 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>08:21</t>
+          <t>2017-09-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>08:21</t>
+          <t>2017-09-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,26 +1184,43 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>gammal grannaturskog</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>1 substratenheter # 1 gammal granlåga</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134135946</v>
+        <v>134135925</v>
       </c>
       <c r="B7" t="n">
-        <v>79366</v>
+        <v>83222</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1239,21 +1228,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1263,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574239</v>
+        <v>574151</v>
       </c>
       <c r="R7" t="n">
-        <v>7150694</v>
+        <v>7150432</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1298,7 +1287,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1308,7 +1297,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134135937</v>
+        <v>134135940</v>
       </c>
       <c r="B8" t="n">
-        <v>79366</v>
+        <v>83222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,21 +1335,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1370,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574222</v>
+        <v>574229</v>
       </c>
       <c r="R8" t="n">
-        <v>7150559</v>
+        <v>7150560</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1405,7 +1394,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1415,7 +1404,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,10 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134135917</v>
+        <v>134135949</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>83222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,39 +1442,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574134</v>
+        <v>574260</v>
       </c>
       <c r="R9" t="n">
-        <v>7150487</v>
+        <v>7150754</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1517,7 +1501,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1527,7 +1511,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134135906</v>
+        <v>134135930</v>
       </c>
       <c r="B10" t="n">
-        <v>79366</v>
+        <v>83363</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1589,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574296</v>
+        <v>574173</v>
       </c>
       <c r="R10" t="n">
-        <v>7150727</v>
+        <v>7150455</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1624,7 +1608,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1634,7 +1618,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,32 +1645,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134135939</v>
+        <v>134135914</v>
       </c>
       <c r="B11" t="n">
-        <v>78725</v>
+        <v>96413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>498</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1696,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574223</v>
+        <v>574169</v>
       </c>
       <c r="R11" t="n">
-        <v>7150560</v>
+        <v>7150498</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1731,7 +1715,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1741,7 +1725,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,14 +1752,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134135908</v>
+        <v>134135905</v>
       </c>
       <c r="B12" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1803,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574266</v>
+        <v>574318</v>
       </c>
       <c r="R12" t="n">
-        <v>7150700</v>
+        <v>7150754</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1838,7 +1822,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1848,7 +1832,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1875,32 +1859,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134135940</v>
+        <v>134135906</v>
       </c>
       <c r="B13" t="n">
-        <v>83215</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1910,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574229</v>
+        <v>574296</v>
       </c>
       <c r="R13" t="n">
-        <v>7150560</v>
+        <v>7150727</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1945,7 +1929,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1955,7 +1939,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,14 +1966,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134135942</v>
+        <v>134135907</v>
       </c>
       <c r="B14" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2017,10 +2001,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574227</v>
+        <v>574313</v>
       </c>
       <c r="R14" t="n">
-        <v>7150564</v>
+        <v>7150743</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2052,7 +2036,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2046,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,14 +2073,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134135913</v>
+        <v>134135908</v>
       </c>
       <c r="B15" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2124,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574255</v>
+        <v>574266</v>
       </c>
       <c r="R15" t="n">
-        <v>7150568</v>
+        <v>7150700</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2159,7 +2143,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2169,7 +2153,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2196,14 +2180,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134135926</v>
+        <v>134135911</v>
       </c>
       <c r="B16" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2231,10 +2215,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574150</v>
+        <v>574260</v>
       </c>
       <c r="R16" t="n">
-        <v>7150432</v>
+        <v>7150657</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2266,7 +2250,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2276,7 +2260,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2303,14 +2287,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134135929</v>
+        <v>134135912</v>
       </c>
       <c r="B17" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2338,10 +2322,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574169</v>
+        <v>574254</v>
       </c>
       <c r="R17" t="n">
-        <v>7150449</v>
+        <v>7150573</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2373,7 +2357,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2383,7 +2367,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2410,14 +2394,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134135941</v>
+        <v>134135913</v>
       </c>
       <c r="B18" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2445,10 +2429,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574230</v>
+        <v>574255</v>
       </c>
       <c r="R18" t="n">
-        <v>7150560</v>
+        <v>7150568</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2480,7 +2464,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2490,7 +2474,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,14 +2501,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134135911</v>
+        <v>134135915</v>
       </c>
       <c r="B19" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2552,10 +2536,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574260</v>
+        <v>574168</v>
       </c>
       <c r="R19" t="n">
-        <v>7150657</v>
+        <v>7150497</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2587,7 +2571,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2597,7 +2581,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,14 +2608,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134135945</v>
+        <v>134135918</v>
       </c>
       <c r="B20" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2659,10 +2643,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574227</v>
+        <v>574130</v>
       </c>
       <c r="R20" t="n">
-        <v>7150576</v>
+        <v>7150486</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2694,7 +2678,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2704,7 +2688,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2731,14 +2715,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134135951</v>
+        <v>134135921</v>
       </c>
       <c r="B21" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2766,10 +2750,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574261</v>
+        <v>574121</v>
       </c>
       <c r="R21" t="n">
-        <v>7150764</v>
+        <v>7150461</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2801,7 +2785,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2811,7 +2795,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2838,14 +2822,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134135912</v>
+        <v>134135923</v>
       </c>
       <c r="B22" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2873,10 +2857,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574254</v>
+        <v>574134</v>
       </c>
       <c r="R22" t="n">
-        <v>7150573</v>
+        <v>7150457</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2908,7 +2892,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2918,7 +2902,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2945,32 +2929,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134135925</v>
+        <v>134135926</v>
       </c>
       <c r="B23" t="n">
-        <v>83215</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2980,7 +2964,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574151</v>
+        <v>574150</v>
       </c>
       <c r="R23" t="n">
         <v>7150432</v>
@@ -3052,32 +3036,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134135930</v>
+        <v>134135929</v>
       </c>
       <c r="B24" t="n">
-        <v>83356</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3087,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574173</v>
+        <v>574169</v>
       </c>
       <c r="R24" t="n">
-        <v>7150455</v>
+        <v>7150449</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3122,7 +3106,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3132,7 +3116,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3159,54 +3143,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134135936</v>
+        <v>134135931</v>
       </c>
       <c r="B25" t="n">
-        <v>58079</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574224</v>
+        <v>574171</v>
       </c>
       <c r="R25" t="n">
-        <v>7150555</v>
+        <v>7150453</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3238,7 +3213,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3248,7 +3223,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3275,14 +3250,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134135905</v>
+        <v>134135934</v>
       </c>
       <c r="B26" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3310,10 +3285,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574318</v>
+        <v>574184</v>
       </c>
       <c r="R26" t="n">
-        <v>7150754</v>
+        <v>7150477</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3345,7 +3320,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3355,7 +3330,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3382,14 +3357,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134135907</v>
+        <v>134135937</v>
       </c>
       <c r="B27" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3417,10 +3392,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574313</v>
+        <v>574222</v>
       </c>
       <c r="R27" t="n">
-        <v>7150743</v>
+        <v>7150559</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3452,7 +3427,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3462,7 +3437,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3489,32 +3464,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134135949</v>
+        <v>134135941</v>
       </c>
       <c r="B28" t="n">
-        <v>83215</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3524,10 +3499,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574260</v>
+        <v>574230</v>
       </c>
       <c r="R28" t="n">
-        <v>7150754</v>
+        <v>7150560</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3559,7 +3534,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3569,7 +3544,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3596,32 +3571,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134135916</v>
+        <v>134135942</v>
       </c>
       <c r="B29" t="n">
-        <v>91967</v>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3631,10 +3606,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574136</v>
+        <v>574227</v>
       </c>
       <c r="R29" t="n">
-        <v>7150487</v>
+        <v>7150564</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3666,7 +3641,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3676,7 +3651,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3703,14 +3678,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134135918</v>
+        <v>134135943</v>
       </c>
       <c r="B30" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3738,10 +3713,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574130</v>
+        <v>574228</v>
       </c>
       <c r="R30" t="n">
-        <v>7150486</v>
+        <v>7150569</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3773,7 +3748,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3783,7 +3758,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3810,14 +3785,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134135921</v>
+        <v>134135945</v>
       </c>
       <c r="B31" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3845,10 +3820,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574121</v>
+        <v>574227</v>
       </c>
       <c r="R31" t="n">
-        <v>7150461</v>
+        <v>7150576</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3880,7 +3855,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3890,7 +3865,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3917,14 +3892,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134135943</v>
+        <v>134135946</v>
       </c>
       <c r="B32" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3952,10 +3927,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574228</v>
+        <v>574239</v>
       </c>
       <c r="R32" t="n">
-        <v>7150569</v>
+        <v>7150694</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3987,7 +3962,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3997,7 +3972,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4024,32 +3999,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134135935</v>
+        <v>134135947</v>
       </c>
       <c r="B33" t="n">
-        <v>78375</v>
+        <v>79373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4059,10 +4034,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574222</v>
+        <v>574258</v>
       </c>
       <c r="R33" t="n">
-        <v>7150554</v>
+        <v>7150736</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4094,7 +4069,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4104,7 +4079,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4131,14 +4106,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134135931</v>
+        <v>134135950</v>
       </c>
       <c r="B34" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4166,10 +4141,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574171</v>
+        <v>574260</v>
       </c>
       <c r="R34" t="n">
-        <v>7150453</v>
+        <v>7150754</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4201,7 +4176,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4211,7 +4186,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4238,14 +4213,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134135923</v>
+        <v>134135951</v>
       </c>
       <c r="B35" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4273,10 +4248,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574134</v>
+        <v>574261</v>
       </c>
       <c r="R35" t="n">
-        <v>7150457</v>
+        <v>7150764</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4308,7 +4283,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4318,7 +4293,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4345,42 +4320,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134135909</v>
+        <v>134135917</v>
       </c>
       <c r="B36" t="n">
-        <v>58678</v>
+        <v>57972</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103056</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4389,10 +4360,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574325</v>
+        <v>574134</v>
       </c>
       <c r="R36" t="n">
-        <v>7150650</v>
+        <v>7150487</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4424,7 +4395,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4434,7 +4405,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4461,10 +4432,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134135915</v>
+        <v>134135910</v>
       </c>
       <c r="B37" t="n">
-        <v>79366</v>
+        <v>58519</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4472,34 +4443,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>102990</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574168</v>
+        <v>574267</v>
       </c>
       <c r="R37" t="n">
-        <v>7150497</v>
+        <v>7150654</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4531,7 +4511,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4541,7 +4521,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4568,10 +4548,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134135950</v>
+        <v>134135924</v>
       </c>
       <c r="B38" t="n">
-        <v>79366</v>
+        <v>58410</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4579,34 +4559,43 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574260</v>
+        <v>574156</v>
       </c>
       <c r="R38" t="n">
-        <v>7150754</v>
+        <v>7150461</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4638,7 +4627,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4648,7 +4637,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4675,45 +4664,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134135922</v>
+        <v>134135927</v>
       </c>
       <c r="B39" t="n">
-        <v>98053</v>
+        <v>58136</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574134</v>
+        <v>574156</v>
       </c>
       <c r="R39" t="n">
-        <v>7150460</v>
+        <v>7150451</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4745,7 +4743,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4755,7 +4753,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4782,10 +4780,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134135928</v>
+        <v>134135936</v>
       </c>
       <c r="B40" t="n">
-        <v>91967</v>
+        <v>58079</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4793,34 +4791,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rävelmyrbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574159</v>
+        <v>574224</v>
       </c>
       <c r="R40" t="n">
-        <v>7150451</v>
+        <v>7150555</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4852,7 +4859,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4862,7 +4869,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4889,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134135910</v>
+        <v>134135909</v>
       </c>
       <c r="B41" t="n">
-        <v>58519</v>
+        <v>58678</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4900,21 +4907,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102990</v>
+        <v>103056</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pallas, 1776</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4933,10 +4940,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574267</v>
+        <v>574325</v>
       </c>
       <c r="R41" t="n">
-        <v>7150654</v>
+        <v>7150650</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4968,7 +4975,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4978,7 +4985,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5005,10 +5012,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134135914</v>
+        <v>134135922</v>
       </c>
       <c r="B42" t="n">
-        <v>96406</v>
+        <v>98060</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5016,21 +5023,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2809</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5040,10 +5047,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574169</v>
+        <v>574134</v>
       </c>
       <c r="R42" t="n">
-        <v>7150498</v>
+        <v>7150460</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5075,7 +5082,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5085,7 +5092,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5109,6 +5116,220 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134135904</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101293</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Rävelmyrbäcken, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>574317</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7150756</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134135935</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78382</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Rävelmyrbäcken, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>574222</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7150554</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
